--- a/sheets/대금율보/검수/경기 방아타령.xlsx
+++ b/sheets/대금율보/검수/경기 방아타령.xlsx
@@ -3003,18 +3003,13 @@
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
@@ -3026,8 +3021,7 @@
         <is>
           <t xml:space="preserve">汰
 㴌
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/경기 방아타령.xlsx
+++ b/sheets/대금율보/검수/경기 방아타령.xlsx
@@ -2724,22 +2724,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="90.2" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="90.2" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="90.2" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3342,6 +3342,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>